--- a/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
+++ b/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,6 +1137,104 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>狂暴猎杀</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>14</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>终焉冲撞</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
+++ b/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,6 +1235,55 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>木桩</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stationary</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
+++ b/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,6 +1284,153 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>孢子仆从索敌</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MinionSeekAttack</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>噬菌体追爆</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MinionSeekExplode</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>15</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>菌丝体固着</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stationary</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
+++ b/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,31 @@
           <t>wanderStrength</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rangedSpeed</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rangedCount</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rangedSpreadDeg</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rangedRadius</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rangedHoming</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +594,31 @@
           <t>float</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -644,6 +694,31 @@
       <c r="O3" t="inlineStr">
         <is>
           <t>游走强度</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>远程弹体速度(u/s),0=不发射弹体</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>一次齐射弹数,0/1=单发</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>齐射张角(度),0=同向</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>弹体碰撞半径,0=用内核默认</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>弹体追踪强度0-1</t>
         </is>
       </c>
     </row>
@@ -695,6 +770,21 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -743,6 +833,21 @@
       </c>
       <c r="O5" t="n">
         <v>0.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -793,6 +898,21 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -842,6 +962,21 @@
       <c r="O7" t="n">
         <v>0.5</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -891,6 +1026,21 @@
       <c r="O8" t="n">
         <v>0.6</v>
       </c>
+      <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -940,6 +1090,21 @@
       <c r="O9" t="n">
         <v>0.7</v>
       </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -963,16 +1128,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -987,6 +1152,21 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1038,6 +1218,21 @@
       <c r="O11" t="n">
         <v>0.4</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1087,6 +1282,21 @@
       <c r="O12" t="n">
         <v>0.9</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1136,6 +1346,21 @@
       <c r="O13" t="n">
         <v>0.5</v>
       </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1185,6 +1410,21 @@
       <c r="O14" t="n">
         <v>0.6</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1234,6 +1474,21 @@
       <c r="O15" t="n">
         <v>0.5</v>
       </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1283,6 +1538,21 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1332,6 +1602,21 @@
       <c r="O17" t="n">
         <v>0.5</v>
       </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1381,6 +1666,21 @@
       <c r="O18" t="n">
         <v>0.4</v>
       </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1430,6 +1730,85 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>追踪投射</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.55</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
+++ b/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,56 @@
           <t>rangedHoming</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>zoneMode</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>zoneRadius</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>zoneSeconds</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>zoneDamagePerTick</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>zoneTickInterval</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>zoneCooldown</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>summonArchetypeId</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>summonCount</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>summonCooldown</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>summonHealth</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -619,6 +669,56 @@
           <t>float</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -719,6 +819,56 @@
       <c r="T3" t="inlineStr">
         <is>
           <t>弹体追踪强度0-1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>区域模式 0=无 1=丢玩家脚下 2=钉自己脚下 3=跟随自己(光环)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>区域半径</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>区域持续秒数</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>区域每跳伤害</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>区域跳伤间隔(秒)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>两次布场间隔(秒),光环设得略短于持续即常驻</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>召唤物行为原型id,&lt;0=不召唤</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>每次召唤数量</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>召唤间隔(秒)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>召唤物生命,0=取宿主生命的1成</t>
         </is>
       </c>
     </row>
@@ -785,6 +935,36 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -847,6 +1027,36 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -913,6 +1123,36 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -977,6 +1217,36 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1041,6 +1311,36 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1105,6 +1405,36 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1169,6 +1499,36 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1233,6 +1593,36 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1297,6 +1687,36 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1361,6 +1781,36 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1425,6 +1875,36 @@
       <c r="T14" t="n">
         <v>0</v>
       </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1489,6 +1969,36 @@
       <c r="T15" t="n">
         <v>0</v>
       </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1553,6 +2063,36 @@
       <c r="T16" t="n">
         <v>0</v>
       </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1617,6 +2157,36 @@
       <c r="T17" t="n">
         <v>0</v>
       </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1681,6 +2251,36 @@
       <c r="T18" t="n">
         <v>0</v>
       </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1745,6 +2345,36 @@
       <c r="T19" t="n">
         <v>0</v>
       </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1809,6 +2439,318 @@
       <c r="T20" t="n">
         <v>0.55</v>
       </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>污染孢团</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>酸沼投手</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" t="n">
+        <v>13</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>19</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>孵化巢</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Stationary</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
+++ b/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,6 +567,11 @@
           <t>summonHealth</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>summonMaxGeneration</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -719,6 +724,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -869,6 +879,11 @@
       <c r="AD3" t="inlineStr">
         <is>
           <t>召唤物生命,0=取宿主生命的1成</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>这支血统最多召到第几代,1=只有原生能召</t>
         </is>
       </c>
     </row>
@@ -965,6 +980,9 @@
       <c r="AD4" t="n">
         <v>0</v>
       </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1057,6 +1075,9 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1153,6 +1174,9 @@
       <c r="AD6" t="n">
         <v>0</v>
       </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1247,6 +1271,9 @@
       <c r="AD7" t="n">
         <v>0</v>
       </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1341,6 +1368,9 @@
       <c r="AD8" t="n">
         <v>0</v>
       </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1435,6 +1465,9 @@
       <c r="AD9" t="n">
         <v>0</v>
       </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1529,6 +1562,9 @@
       <c r="AD10" t="n">
         <v>0</v>
       </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1623,6 +1659,9 @@
       <c r="AD11" t="n">
         <v>0</v>
       </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1717,6 +1756,9 @@
       <c r="AD12" t="n">
         <v>0</v>
       </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1811,6 +1853,9 @@
       <c r="AD13" t="n">
         <v>0</v>
       </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1905,6 +1950,9 @@
       <c r="AD14" t="n">
         <v>0</v>
       </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1999,6 +2047,9 @@
       <c r="AD15" t="n">
         <v>0</v>
       </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -2093,6 +2144,9 @@
       <c r="AD16" t="n">
         <v>0</v>
       </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -2187,6 +2241,9 @@
       <c r="AD17" t="n">
         <v>0</v>
       </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2281,6 +2338,9 @@
       <c r="AD18" t="n">
         <v>0</v>
       </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -2375,6 +2435,9 @@
       <c r="AD19" t="n">
         <v>0</v>
       </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -2469,6 +2532,9 @@
       <c r="AD20" t="n">
         <v>0</v>
       </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -2563,6 +2629,9 @@
       <c r="AD21" t="n">
         <v>0</v>
       </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -2657,6 +2726,9 @@
       <c r="AD22" t="n">
         <v>0</v>
       </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -2751,6 +2823,9 @@
       <c r="AD23" t="n">
         <v>8</v>
       </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
